--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/9.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/9.xlsx
@@ -426,13 +426,13 @@
         <v>-18.25974267730904</v>
       </c>
       <c r="E2">
-        <v>-19.03684186641832</v>
+        <v>-16.38781589767738</v>
       </c>
       <c r="F2">
-        <v>-1.736097520239128</v>
+        <v>-0.5993297617447697</v>
       </c>
       <c r="G2">
-        <v>-12.40965393662824</v>
+        <v>-10.76822917898342</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.16997662381502</v>
       </c>
       <c r="E3">
-        <v>-19.55074215375677</v>
+        <v>-15.66630319098328</v>
       </c>
       <c r="F3">
-        <v>-1.798581273432295</v>
+        <v>-0.4487060601589299</v>
       </c>
       <c r="G3">
-        <v>-12.18007422457086</v>
+        <v>-10.21686775105442</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.91398141797096</v>
       </c>
       <c r="E4">
-        <v>-19.81880517264081</v>
+        <v>-16.07672331877245</v>
       </c>
       <c r="F4">
-        <v>-1.472668402474858</v>
+        <v>-0.4512872529860532</v>
       </c>
       <c r="G4">
-        <v>-11.97925984270421</v>
+        <v>-9.905517564177046</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.48649996246489</v>
       </c>
       <c r="E5">
-        <v>-20.39623542183287</v>
+        <v>-17.9923221657051</v>
       </c>
       <c r="F5">
-        <v>-1.655267085808758</v>
+        <v>-0.4289287884170918</v>
       </c>
       <c r="G5">
-        <v>-12.31683286079816</v>
+        <v>-10.1898139729075</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.90107053507262</v>
       </c>
       <c r="E6">
-        <v>-20.95307922818606</v>
+        <v>-17.57109709893363</v>
       </c>
       <c r="F6">
-        <v>-1.627779370281662</v>
+        <v>-0.3342215432550243</v>
       </c>
       <c r="G6">
-        <v>-12.14222806796592</v>
+        <v>-9.534554383774012</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.17264128285261</v>
       </c>
       <c r="E7">
-        <v>-21.50616892958688</v>
+        <v>-18.50259967383742</v>
       </c>
       <c r="F7">
-        <v>-1.159075011531854</v>
+        <v>-0.2818985446245963</v>
       </c>
       <c r="G7">
-        <v>-11.70157128287015</v>
+        <v>-10.6949370112895</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.33682210131501</v>
       </c>
       <c r="E8">
-        <v>-21.90483313885214</v>
+        <v>-19.12827628510719</v>
       </c>
       <c r="F8">
-        <v>-1.083242117642574</v>
+        <v>-0.1739167118326667</v>
       </c>
       <c r="G8">
-        <v>-11.24979437530796</v>
+        <v>-10.25232700432556</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.41289487295862</v>
       </c>
       <c r="E9">
-        <v>-22.54852401972443</v>
+        <v>-20.22601008388454</v>
       </c>
       <c r="F9">
-        <v>-1.209806716381504</v>
+        <v>0.269275587645722</v>
       </c>
       <c r="G9">
-        <v>-10.97635655594632</v>
+        <v>-10.13978831926357</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.41455209776333</v>
       </c>
       <c r="E10">
-        <v>-22.9924186273783</v>
+        <v>-21.0463884351141</v>
       </c>
       <c r="F10">
-        <v>-1.099989221424971</v>
+        <v>-0.2048413237139779</v>
       </c>
       <c r="G10">
-        <v>-11.5138997667944</v>
+        <v>-9.106077095717222</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.37203715406358</v>
       </c>
       <c r="E11">
-        <v>-24.04097772690636</v>
+        <v>-20.98069839115884</v>
       </c>
       <c r="F11">
-        <v>-1.118469269814026</v>
+        <v>-0.09807056406494122</v>
       </c>
       <c r="G11">
-        <v>-11.27114408349073</v>
+        <v>-8.56213128979619</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.29511451600209</v>
       </c>
       <c r="E12">
-        <v>-25.12311093272728</v>
+        <v>-21.76665128298209</v>
       </c>
       <c r="F12">
-        <v>-0.776814933101189</v>
+        <v>0.01253553665905717</v>
       </c>
       <c r="G12">
-        <v>-10.34097679277616</v>
+        <v>-7.966176813453209</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.18277832290328</v>
       </c>
       <c r="E13">
-        <v>-25.02938963466453</v>
+        <v>-23.33816761786393</v>
       </c>
       <c r="F13">
-        <v>-0.8517556752976546</v>
+        <v>0.2280924738481417</v>
       </c>
       <c r="G13">
-        <v>-10.68296607861949</v>
+        <v>-7.88750169871243</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.058305478530492</v>
       </c>
       <c r="E14">
-        <v>-25.13675069643838</v>
+        <v>-23.8418652532631</v>
       </c>
       <c r="F14">
-        <v>-0.7413400990763001</v>
+        <v>0.6309093177466797</v>
       </c>
       <c r="G14">
-        <v>-9.933435394709718</v>
+        <v>-7.294678998449599</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.925543907761202</v>
       </c>
       <c r="E15">
-        <v>-27.17947739418837</v>
+        <v>-25.03798467833109</v>
       </c>
       <c r="F15">
-        <v>-0.6079804025322049</v>
+        <v>0.1722132939574955</v>
       </c>
       <c r="G15">
-        <v>-9.29676782932478</v>
+        <v>-7.129837004412669</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.78081304620958</v>
       </c>
       <c r="E16">
-        <v>-27.25800113348137</v>
+        <v>-26.38756050209701</v>
       </c>
       <c r="F16">
-        <v>-0.3641247781286837</v>
+        <v>0.8339214589877686</v>
       </c>
       <c r="G16">
-        <v>-9.128760953752307</v>
+        <v>-6.412643729330497</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.647535265887297</v>
       </c>
       <c r="E17">
-        <v>-28.04547106409719</v>
+        <v>-26.72359138736218</v>
       </c>
       <c r="F17">
-        <v>-0.2886364850789675</v>
+        <v>0.7472775421245514</v>
       </c>
       <c r="G17">
-        <v>-8.497598825599177</v>
+        <v>-5.580011731293941</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.53493119143519</v>
       </c>
       <c r="E18">
-        <v>-28.60484628742066</v>
+        <v>-27.40373648399622</v>
       </c>
       <c r="F18">
-        <v>-0.1359692011104214</v>
+        <v>1.063359348745564</v>
       </c>
       <c r="G18">
-        <v>-8.087428854374556</v>
+        <v>-6.177267252033856</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.445344459013837</v>
       </c>
       <c r="E19">
-        <v>-30.08192582534655</v>
+        <v>-27.68080210920751</v>
       </c>
       <c r="F19">
-        <v>0.4595590353753936</v>
+        <v>1.07855823385213</v>
       </c>
       <c r="G19">
-        <v>-7.678934019192805</v>
+        <v>-4.699161637477899</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.404265184274664</v>
       </c>
       <c r="E20">
-        <v>-30.74379852935964</v>
+        <v>-29.01029867922342</v>
       </c>
       <c r="F20">
-        <v>0.2205626141566942</v>
+        <v>1.328226512321095</v>
       </c>
       <c r="G20">
-        <v>-6.554424463140865</v>
+        <v>-3.921732986308689</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.4244490942948</v>
       </c>
       <c r="E21">
-        <v>-31.59896914639013</v>
+        <v>-28.57584593987555</v>
       </c>
       <c r="F21">
-        <v>0.5024684668404079</v>
+        <v>1.791553938259332</v>
       </c>
       <c r="G21">
-        <v>-7.441336165839312</v>
+        <v>-3.533975408384933</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5080247091072309</v>
       </c>
       <c r="E22">
-        <v>-31.14541077520389</v>
+        <v>-29.89831658246855</v>
       </c>
       <c r="F22">
-        <v>0.2960467653693963</v>
+        <v>1.679666353163202</v>
       </c>
       <c r="G22">
-        <v>-7.242180367287836</v>
+        <v>-3.944092410880927</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.3277025387945248</v>
       </c>
       <c r="E23">
-        <v>-32.52840220867241</v>
+        <v>-30.55909113153478</v>
       </c>
       <c r="F23">
-        <v>0.8501674004914724</v>
+        <v>1.43426582355346</v>
       </c>
       <c r="G23">
-        <v>-6.580594325628804</v>
+        <v>-3.540037017267339</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.076420310045093</v>
       </c>
       <c r="E24">
-        <v>-32.7918892045717</v>
+        <v>-30.2241787793495</v>
       </c>
       <c r="F24">
-        <v>0.5996666127826935</v>
+        <v>1.708654242056768</v>
       </c>
       <c r="G24">
-        <v>-5.966723176827287</v>
+        <v>-2.501035541949234</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.741074171059615</v>
       </c>
       <c r="E25">
-        <v>-33.1184306725538</v>
+        <v>-30.97402161943559</v>
       </c>
       <c r="F25">
-        <v>0.6846248019812137</v>
+        <v>1.912479011720003</v>
       </c>
       <c r="G25">
-        <v>-6.420777739720487</v>
+        <v>-3.356460646023673</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.312681342504132</v>
       </c>
       <c r="E26">
-        <v>-32.56259671590433</v>
+        <v>-30.61918398161656</v>
       </c>
       <c r="F26">
-        <v>0.6986101288426777</v>
+        <v>1.71435672325764</v>
       </c>
       <c r="G26">
-        <v>-6.425111243831393</v>
+        <v>-3.219367644696914</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.788483811047201</v>
       </c>
       <c r="E27">
-        <v>-33.16863333540284</v>
+        <v>-31.87412601980719</v>
       </c>
       <c r="F27">
-        <v>0.9987582884708421</v>
+        <v>2.199736946193205</v>
       </c>
       <c r="G27">
-        <v>-5.892312044741089</v>
+        <v>-3.623767335046586</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.173344009061655</v>
       </c>
       <c r="E28">
-        <v>-32.93865025444929</v>
+        <v>-32.13410571258755</v>
       </c>
       <c r="F28">
-        <v>0.3383266376082831</v>
+        <v>1.74870746271693</v>
       </c>
       <c r="G28">
-        <v>-6.003486785040893</v>
+        <v>-3.540490562006219</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.465665900656881</v>
       </c>
       <c r="E29">
-        <v>-33.47733714426872</v>
+        <v>-30.96035015640643</v>
       </c>
       <c r="F29">
-        <v>0.7683379549733261</v>
+        <v>1.886334079752845</v>
       </c>
       <c r="G29">
-        <v>-6.318465329829311</v>
+        <v>-2.849258585043013</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.666782033760164</v>
       </c>
       <c r="E30">
-        <v>-32.60757578398551</v>
+        <v>-31.32089140723812</v>
       </c>
       <c r="F30">
-        <v>1.138349792986198</v>
+        <v>1.649750692778501</v>
       </c>
       <c r="G30">
-        <v>-6.2616464367388</v>
+        <v>-2.796978449886843</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.780305196254466</v>
       </c>
       <c r="E31">
-        <v>-32.45771272941268</v>
+        <v>-30.86585448928837</v>
       </c>
       <c r="F31">
-        <v>0.9950869641416348</v>
+        <v>1.794159982108539</v>
       </c>
       <c r="G31">
-        <v>-6.011905502347259</v>
+        <v>-3.449258548034984</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.805261293491008</v>
       </c>
       <c r="E32">
-        <v>-32.87375722191937</v>
+        <v>-30.08599013076844</v>
       </c>
       <c r="F32">
-        <v>0.8893491786438891</v>
+        <v>1.585151289238584</v>
       </c>
       <c r="G32">
-        <v>-6.348942212063841</v>
+        <v>-3.374056195564899</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.74177927246738</v>
       </c>
       <c r="E33">
-        <v>-31.96141688477904</v>
+        <v>-29.51960256544409</v>
       </c>
       <c r="F33">
-        <v>0.3746000178094707</v>
+        <v>1.395602603395196</v>
       </c>
       <c r="G33">
-        <v>-5.985417827487551</v>
+        <v>-2.922474610189535</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.590084189798469</v>
       </c>
       <c r="E34">
-        <v>-31.68745779273701</v>
+        <v>-29.2894791017963</v>
       </c>
       <c r="F34">
-        <v>0.603924421233083</v>
+        <v>1.253988225682203</v>
       </c>
       <c r="G34">
-        <v>-6.083088852532669</v>
+        <v>-4.004251644420562</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.351526838511829</v>
       </c>
       <c r="E35">
-        <v>-31.17758558302839</v>
+        <v>-29.38186450002678</v>
       </c>
       <c r="F35">
-        <v>0.7612239357180839</v>
+        <v>1.660872353528487</v>
       </c>
       <c r="G35">
-        <v>-6.097694979451934</v>
+        <v>-4.172721996368534</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.031110258591973</v>
       </c>
       <c r="E36">
-        <v>-30.86162489456521</v>
+        <v>-28.41767087126163</v>
       </c>
       <c r="F36">
-        <v>0.6233985105054966</v>
+        <v>1.779408415399485</v>
       </c>
       <c r="G36">
-        <v>-6.859729593863532</v>
+        <v>-3.818781641128433</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.630943380238264</v>
       </c>
       <c r="E37">
-        <v>-30.60942964860404</v>
+        <v>-27.92758582872952</v>
       </c>
       <c r="F37">
-        <v>0.2056925909090403</v>
+        <v>1.467839554388924</v>
       </c>
       <c r="G37">
-        <v>-6.985301896713628</v>
+        <v>-4.231477558599519</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.156939666341338</v>
       </c>
       <c r="E38">
-        <v>-30.04971252549299</v>
+        <v>-27.05153441804966</v>
       </c>
       <c r="F38">
-        <v>0.50709986898946</v>
+        <v>1.324028346323707</v>
       </c>
       <c r="G38">
-        <v>-6.914774034544994</v>
+        <v>-3.861070549847084</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.620750775524838</v>
       </c>
       <c r="E39">
-        <v>-29.00176250571896</v>
+        <v>-25.92788416252641</v>
       </c>
       <c r="F39">
-        <v>0.953501263786294</v>
+        <v>1.683558023221554</v>
       </c>
       <c r="G39">
-        <v>-7.017182450256809</v>
+        <v>-5.15339496983022</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.027200044973679</v>
       </c>
       <c r="E40">
-        <v>-28.26744780300518</v>
+        <v>-25.23782170781558</v>
       </c>
       <c r="F40">
-        <v>0.7487536928363402</v>
+        <v>2.022191304016381</v>
       </c>
       <c r="G40">
-        <v>-7.329449658248564</v>
+        <v>-4.908563574473419</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.3865249631739457</v>
       </c>
       <c r="E41">
-        <v>-27.90257959525916</v>
+        <v>-24.86552227422298</v>
       </c>
       <c r="F41">
-        <v>1.086715996034899</v>
+        <v>2.049686474850102</v>
       </c>
       <c r="G41">
-        <v>-6.821337197244604</v>
+        <v>-4.19395583545742</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.2831419576598925</v>
       </c>
       <c r="E42">
-        <v>-28.03761416169388</v>
+        <v>-24.89246669456861</v>
       </c>
       <c r="F42">
-        <v>0.6088424385035037</v>
+        <v>2.069214408003698</v>
       </c>
       <c r="G42">
-        <v>-7.51070864761474</v>
+        <v>-3.899158376276399</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.975634219303637</v>
       </c>
       <c r="E43">
-        <v>-27.14962116505579</v>
+        <v>-24.11247780301346</v>
       </c>
       <c r="F43">
-        <v>0.8851361020332508</v>
+        <v>2.110313028326192</v>
       </c>
       <c r="G43">
-        <v>-7.547118027455644</v>
+        <v>-5.008561913032644</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.681788833371336</v>
       </c>
       <c r="E44">
-        <v>-26.85361293307042</v>
+        <v>-23.76402531354525</v>
       </c>
       <c r="F44">
-        <v>1.253887164859062</v>
+        <v>2.384030469233233</v>
       </c>
       <c r="G44">
-        <v>-7.499866610973627</v>
+        <v>-5.096582697830788</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.384822985118272</v>
       </c>
       <c r="E45">
-        <v>-25.8991283525777</v>
+        <v>-22.64469522222532</v>
       </c>
       <c r="F45">
-        <v>1.042880449813555</v>
+        <v>2.23454494445884</v>
       </c>
       <c r="G45">
-        <v>-7.172903891333047</v>
+        <v>-4.713681690213142</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.08317815822459</v>
       </c>
       <c r="E46">
-        <v>-24.17013433407912</v>
+        <v>-23.15000046589721</v>
       </c>
       <c r="F46">
-        <v>1.00299787283837</v>
+        <v>2.439110274580178</v>
       </c>
       <c r="G46">
-        <v>-7.854627981507466</v>
+        <v>-5.484846789222051</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.772748532284563</v>
       </c>
       <c r="E47">
-        <v>-24.57734377379685</v>
+        <v>-21.58419453673904</v>
       </c>
       <c r="F47">
-        <v>1.235010328484067</v>
+        <v>2.605125042510032</v>
       </c>
       <c r="G47">
-        <v>-7.513280941498754</v>
+        <v>-4.716340058281177</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.44038178809669</v>
       </c>
       <c r="E48">
-        <v>-23.13122994113542</v>
+        <v>-20.67005865965467</v>
       </c>
       <c r="F48">
-        <v>1.245328472853337</v>
+        <v>2.573501288540758</v>
       </c>
       <c r="G48">
-        <v>-8.043014575419694</v>
+        <v>-5.18482528918006</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.08688439916207</v>
       </c>
       <c r="E49">
-        <v>-23.44913334494789</v>
+        <v>-20.18891282481371</v>
       </c>
       <c r="F49">
-        <v>1.050456698079559</v>
+        <v>2.372198069251645</v>
       </c>
       <c r="G49">
-        <v>-8.035188445764856</v>
+        <v>-5.293139718133935</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.711512738863823</v>
       </c>
       <c r="E50">
-        <v>-22.11087417772713</v>
+        <v>-19.28994280718102</v>
       </c>
       <c r="F50">
-        <v>1.256246355222235</v>
+        <v>2.465275087365003</v>
       </c>
       <c r="G50">
-        <v>-7.61977457040603</v>
+        <v>-4.893292027900761</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.304534518044444</v>
       </c>
       <c r="E51">
-        <v>-21.89135187173131</v>
+        <v>-18.51109961954981</v>
       </c>
       <c r="F51">
-        <v>1.299445715278229</v>
+        <v>3.201801396216127</v>
       </c>
       <c r="G51">
-        <v>-8.284389761233495</v>
+        <v>-5.979687273159072</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.868261261873575</v>
       </c>
       <c r="E52">
-        <v>-21.26062601194298</v>
+        <v>-18.63784255007649</v>
       </c>
       <c r="F52">
-        <v>1.523338513641685</v>
+        <v>2.309714316058478</v>
       </c>
       <c r="G52">
-        <v>-7.769199353866574</v>
+        <v>-5.220390479908451</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.404762946384505</v>
       </c>
       <c r="E53">
-        <v>-21.72400664325185</v>
+        <v>-17.7307801493921</v>
       </c>
       <c r="F53">
-        <v>1.173021938997774</v>
+        <v>2.70920940667179</v>
       </c>
       <c r="G53">
-        <v>-8.226869032488658</v>
+        <v>-5.985166226026567</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.907740735216035</v>
       </c>
       <c r="E54">
-        <v>-20.68735290188997</v>
+        <v>-17.49864151481091</v>
       </c>
       <c r="F54">
-        <v>1.192882875847295</v>
+        <v>2.397004359495879</v>
       </c>
       <c r="G54">
-        <v>-7.96194924679956</v>
+        <v>-6.056826294769631</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.378217339798988</v>
       </c>
       <c r="E55">
-        <v>-20.78211574897448</v>
+        <v>-17.47946795586243</v>
       </c>
       <c r="F55">
-        <v>1.169539482436405</v>
+        <v>2.474307605525129</v>
       </c>
       <c r="G55">
-        <v>-8.741437057294197</v>
+        <v>-5.876941181802252</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.816615964077915</v>
       </c>
       <c r="E56">
-        <v>-19.65988743428964</v>
+        <v>-16.79415587038564</v>
       </c>
       <c r="F56">
-        <v>1.244515016063788</v>
+        <v>2.705789906033034</v>
       </c>
       <c r="G56">
-        <v>-8.242481565251861</v>
+        <v>-5.722183109477942</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.215903061407698</v>
       </c>
       <c r="E57">
-        <v>-19.27172475624817</v>
+        <v>-16.56862427938164</v>
       </c>
       <c r="F57">
-        <v>1.055514709441053</v>
+        <v>2.789796301085737</v>
       </c>
       <c r="G57">
-        <v>-8.998861767882385</v>
+        <v>-5.9629392232759</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.571128936307582</v>
       </c>
       <c r="E58">
-        <v>-18.70404431159463</v>
+        <v>-15.19319539750593</v>
       </c>
       <c r="F58">
-        <v>1.111663108737609</v>
+        <v>2.206382109498462</v>
       </c>
       <c r="G58">
-        <v>-8.224316601877879</v>
+        <v>-6.918670546644717</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.876401515691612</v>
       </c>
       <c r="E59">
-        <v>-18.6653620866211</v>
+        <v>-14.32560317627239</v>
       </c>
       <c r="F59">
-        <v>1.389205950310778</v>
+        <v>2.484958753590325</v>
       </c>
       <c r="G59">
-        <v>-9.041465178427266</v>
+        <v>-7.437538970105768</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.12375906351746</v>
       </c>
       <c r="E60">
-        <v>-18.24579896981045</v>
+        <v>-14.99344440902759</v>
       </c>
       <c r="F60">
-        <v>1.197041280209349</v>
+        <v>2.527111057249181</v>
       </c>
       <c r="G60">
-        <v>-8.732342988697818</v>
+        <v>-6.418559674209176</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.30617946519489</v>
       </c>
       <c r="E61">
-        <v>-17.65267755818181</v>
+        <v>-14.58574136564302</v>
       </c>
       <c r="F61">
-        <v>0.8162971141258063</v>
+        <v>2.096215871865351</v>
       </c>
       <c r="G61">
-        <v>-9.061318520026274</v>
+        <v>-6.772450371266187</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.41763685606432</v>
       </c>
       <c r="E62">
-        <v>-17.30580550614228</v>
+        <v>-14.50763877443273</v>
       </c>
       <c r="F62">
-        <v>1.107504704375556</v>
+        <v>1.873118306208582</v>
       </c>
       <c r="G62">
-        <v>-8.814931168266018</v>
+        <v>-6.997660163211727</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.45524288312628</v>
       </c>
       <c r="E63">
-        <v>-17.13194380356579</v>
+        <v>-14.56378732365383</v>
       </c>
       <c r="F63">
-        <v>1.057882183478254</v>
+        <v>2.370306078103651</v>
       </c>
       <c r="G63">
-        <v>-9.372777954906448</v>
+        <v>-6.977621431062518</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.41294895453114</v>
       </c>
       <c r="E64">
-        <v>-17.53771771702309</v>
+        <v>-13.42280659810323</v>
       </c>
       <c r="F64">
-        <v>0.9059844528269088</v>
+        <v>2.104632084677793</v>
       </c>
       <c r="G64">
-        <v>-9.287054688712558</v>
+        <v>-7.271174125120774</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.28482965380948</v>
       </c>
       <c r="E65">
-        <v>-17.4195290738969</v>
+        <v>-14.1319610992304</v>
       </c>
       <c r="F65">
-        <v>0.7273056040430553</v>
+        <v>1.80082999643588</v>
       </c>
       <c r="G65">
-        <v>-9.21414654430119</v>
+        <v>-7.90130667361119</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.07366946532071</v>
       </c>
       <c r="E66">
-        <v>-15.97028153722216</v>
+        <v>-13.68111528397476</v>
       </c>
       <c r="F66">
-        <v>0.6854374304033599</v>
+        <v>1.710077377254778</v>
       </c>
       <c r="G66">
-        <v>-9.978819663507588</v>
+        <v>-8.465536192051335</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.777234460311343</v>
       </c>
       <c r="E67">
-        <v>-15.56237924098125</v>
+        <v>-14.1799583952377</v>
       </c>
       <c r="F67">
-        <v>0.3272770448223405</v>
+        <v>1.935353549180909</v>
       </c>
       <c r="G67">
-        <v>-9.070627774082705</v>
+        <v>-6.937080490388603</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.393366845069343</v>
       </c>
       <c r="E68">
-        <v>-17.38175707219893</v>
+        <v>-12.92250984668383</v>
       </c>
       <c r="F68">
-        <v>0.3087771156156192</v>
+        <v>1.650663553656386</v>
       </c>
       <c r="G68">
-        <v>-9.063516722264351</v>
+        <v>-7.782693137484642</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.931985849364077</v>
       </c>
       <c r="E69">
-        <v>-15.84303141760662</v>
+        <v>-13.12488735008662</v>
       </c>
       <c r="F69">
-        <v>-0.03525629227805751</v>
+        <v>1.447572717512031</v>
       </c>
       <c r="G69">
-        <v>-9.35091842271064</v>
+        <v>-6.594273499797072</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.397720979627755</v>
       </c>
       <c r="E70">
-        <v>-16.32127450060867</v>
+        <v>-11.76505453269332</v>
       </c>
       <c r="F70">
-        <v>0.004125950785836586</v>
+        <v>1.211514515471062</v>
       </c>
       <c r="G70">
-        <v>-9.130591685435524</v>
+        <v>-6.466112350335266</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.793351525245981</v>
       </c>
       <c r="E71">
-        <v>-16.02851318448679</v>
+        <v>-12.6459604675094</v>
       </c>
       <c r="F71">
-        <v>-0.1128768030225796</v>
+        <v>1.053962348928207</v>
       </c>
       <c r="G71">
-        <v>-9.314330273410615</v>
+        <v>-6.498727844988166</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.135464976424709</v>
       </c>
       <c r="E72">
-        <v>-16.3111352473055</v>
+        <v>-12.1983842104873</v>
       </c>
       <c r="F72">
-        <v>-0.03618075029958176</v>
+        <v>1.020106973175791</v>
       </c>
       <c r="G72">
-        <v>-9.252601841285363</v>
+        <v>-6.223674479403359</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.433821326097906</v>
       </c>
       <c r="E73">
-        <v>-15.91465829098595</v>
+        <v>-13.65551129193539</v>
       </c>
       <c r="F73">
-        <v>-0.3329375737806851</v>
+        <v>1.321399108187222</v>
       </c>
       <c r="G73">
-        <v>-8.681532735761085</v>
+        <v>-7.213977829838785</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.690780762831516</v>
       </c>
       <c r="E74">
-        <v>-15.76612434353436</v>
+        <v>-12.74460421681849</v>
       </c>
       <c r="F74">
-        <v>-0.2774402712627294</v>
+        <v>1.063773532446964</v>
       </c>
       <c r="G74">
-        <v>-9.005585485872645</v>
+        <v>-6.079364488800989</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.92087353318536</v>
       </c>
       <c r="E75">
-        <v>-17.02926065544187</v>
+        <v>-12.82436422951559</v>
       </c>
       <c r="F75">
-        <v>-0.0496897659044361</v>
+        <v>0.9549542202108043</v>
       </c>
       <c r="G75">
-        <v>-7.731280365259761</v>
+        <v>-6.217470517062765</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.132509667718372</v>
       </c>
       <c r="E76">
-        <v>-16.22387155317769</v>
+        <v>-13.55346665864654</v>
       </c>
       <c r="F76">
-        <v>-0.2490819415952911</v>
+        <v>0.9588177257774612</v>
       </c>
       <c r="G76">
-        <v>-8.276004149382521</v>
+        <v>-6.166713232854659</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.325606589265877</v>
       </c>
       <c r="E77">
-        <v>-16.63117156237558</v>
+        <v>-13.98435096047638</v>
       </c>
       <c r="F77">
-        <v>-0.3336905597498298</v>
+        <v>0.8777967668444472</v>
       </c>
       <c r="G77">
-        <v>-7.732429124561889</v>
+        <v>-5.68862410934635</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.51319766892188</v>
       </c>
       <c r="E78">
-        <v>-17.45923020552215</v>
+        <v>-14.1263503199349</v>
       </c>
       <c r="F78">
-        <v>-0.6317330094400779</v>
+        <v>0.4989570174199409</v>
       </c>
       <c r="G78">
-        <v>-8.131700779871229</v>
+        <v>-5.402473795113906</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.705038323485407</v>
       </c>
       <c r="E79">
-        <v>-17.95723102061967</v>
+        <v>-14.92792644708461</v>
       </c>
       <c r="F79">
-        <v>-0.8282201006493151</v>
+        <v>0.4122070695291654</v>
       </c>
       <c r="G79">
-        <v>-7.341533149466904</v>
+        <v>-5.207701158856424</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.8988804249101469</v>
       </c>
       <c r="E80">
-        <v>-17.80873782943415</v>
+        <v>-15.68978785718706</v>
       </c>
       <c r="F80">
-        <v>-0.7890457778035236</v>
+        <v>0.5058216980869403</v>
       </c>
       <c r="G80">
-        <v>-6.93777901549739</v>
+        <v>-4.499257655634548</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.1034580004238942</v>
       </c>
       <c r="E81">
-        <v>-18.55580924342754</v>
+        <v>-14.57852297807479</v>
       </c>
       <c r="F81">
-        <v>-0.6831522592340517</v>
+        <v>0.8119697228135816</v>
       </c>
       <c r="G81">
-        <v>-6.43216932692112</v>
+        <v>-4.499353661455187</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.6730017482200855</v>
       </c>
       <c r="E82">
-        <v>-19.25573471452708</v>
+        <v>-15.65454727245937</v>
       </c>
       <c r="F82">
-        <v>-0.4688229625359159</v>
+        <v>0.4681823400385364</v>
       </c>
       <c r="G82">
-        <v>-6.373013188679883</v>
+        <v>-4.067509548584956</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.435290546760378</v>
       </c>
       <c r="E83">
-        <v>-20.19223672473533</v>
+        <v>-17.58610446179505</v>
       </c>
       <c r="F83">
-        <v>-0.6907251940304447</v>
+        <v>0.5848554036206384</v>
       </c>
       <c r="G83">
-        <v>-6.116545225752543</v>
+        <v>-4.155364806106135</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.178821336329635</v>
       </c>
       <c r="E84">
-        <v>-20.72738461211777</v>
+        <v>-18.29336153231301</v>
       </c>
       <c r="F84">
-        <v>-0.9267436344360799</v>
+        <v>0.6466391863584395</v>
       </c>
       <c r="G84">
-        <v>-6.166037881564648</v>
+        <v>-2.825939102264387</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.896218509569577</v>
       </c>
       <c r="E85">
-        <v>-21.07994442751094</v>
+        <v>-19.29833859799124</v>
       </c>
       <c r="F85">
-        <v>-0.8787380867090429</v>
+        <v>0.423364350077472</v>
       </c>
       <c r="G85">
-        <v>-5.875352119943402</v>
+        <v>-3.388973513764856</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.594145801299084</v>
       </c>
       <c r="E86">
-        <v>-23.20285681451474</v>
+        <v>-19.79717718078018</v>
       </c>
       <c r="F86">
-        <v>-1.118388089808551</v>
+        <v>0.6650173455569494</v>
       </c>
       <c r="G86">
-        <v>-6.285906114450579</v>
+        <v>-3.120236669068977</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.270949713630128</v>
       </c>
       <c r="E87">
-        <v>-23.16876193371099</v>
+        <v>-21.1768628282231</v>
       </c>
       <c r="F87">
-        <v>-0.818734465519858</v>
+        <v>0.3894857800377778</v>
       </c>
       <c r="G87">
-        <v>-5.664612722550016</v>
+        <v>-3.219374265787993</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.918501770177743</v>
       </c>
       <c r="E88">
-        <v>-24.04223664268049</v>
+        <v>-22.08411542481581</v>
       </c>
       <c r="F88">
-        <v>-1.338179641160747</v>
+        <v>0.329221223116711</v>
       </c>
       <c r="G88">
-        <v>-5.703087882807425</v>
+        <v>-2.71327461647191</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.540650628314284</v>
       </c>
       <c r="E89">
-        <v>-25.86162805932019</v>
+        <v>-23.59625440850908</v>
       </c>
       <c r="F89">
-        <v>-1.163794220625603</v>
+        <v>0.07456037431107294</v>
       </c>
       <c r="G89">
-        <v>-5.404940151540663</v>
+        <v>-3.436168650972705</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.13282507162651</v>
       </c>
       <c r="E90">
-        <v>-27.20039441562979</v>
+        <v>-24.2060134336419</v>
       </c>
       <c r="F90">
-        <v>-1.021142726924306</v>
+        <v>-0.1071502991670266</v>
       </c>
       <c r="G90">
-        <v>-5.022827053761365</v>
+        <v>-2.6779775799322</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.680714745494652</v>
       </c>
       <c r="E91">
-        <v>-28.57624444558822</v>
+        <v>-26.1862924748261</v>
       </c>
       <c r="F91">
-        <v>-1.305221387305563</v>
+        <v>0.061078694830511</v>
       </c>
       <c r="G91">
-        <v>-5.667125426614323</v>
+        <v>-2.143691945894763</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>7.178743072999548</v>
       </c>
       <c r="E92">
-        <v>-29.83120686191188</v>
+        <v>-28.10829911247961</v>
       </c>
       <c r="F92">
-        <v>-1.435710790798958</v>
+        <v>0.1890009877426302</v>
       </c>
       <c r="G92">
-        <v>-5.270131426636</v>
+        <v>-3.151302828409498</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>7.614677137641173</v>
       </c>
       <c r="E93">
-        <v>-31.18316466300584</v>
+        <v>-30.39994470524621</v>
       </c>
       <c r="F93">
-        <v>-1.473805750918901</v>
+        <v>-0.4560014918753852</v>
       </c>
       <c r="G93">
-        <v>-5.19967970701477</v>
+        <v>-3.353997600142455</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>7.967885691109613</v>
       </c>
       <c r="E94">
-        <v>-33.30018550532566</v>
+        <v>-30.9740850180717</v>
       </c>
       <c r="F94">
-        <v>-1.488908545406742</v>
+        <v>-0.4929872680429803</v>
       </c>
       <c r="G94">
-        <v>-5.698645130693723</v>
+        <v>-3.455429404920185</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>8.229847764888369</v>
       </c>
       <c r="E95">
-        <v>-35.6801725690339</v>
+        <v>-32.27145659347719</v>
       </c>
       <c r="F95">
-        <v>-1.708409339800555</v>
+        <v>-0.5338390348794407</v>
       </c>
       <c r="G95">
-        <v>-5.223469287259973</v>
+        <v>-3.188344522448403</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>8.382075386321791</v>
       </c>
       <c r="E96">
-        <v>-36.32680469377416</v>
+        <v>-35.14269704601152</v>
       </c>
       <c r="F96">
-        <v>-1.974371605082587</v>
+        <v>-1.023351154420169</v>
       </c>
       <c r="G96">
-        <v>-5.97061306783593</v>
+        <v>-3.680000261576646</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>8.42024694355924</v>
       </c>
       <c r="E97">
-        <v>-38.15204237035776</v>
+        <v>-36.64304161915181</v>
       </c>
       <c r="F97">
-        <v>-1.791369506823523</v>
+        <v>-0.6527279812640314</v>
       </c>
       <c r="G97">
-        <v>-5.965504896068835</v>
+        <v>-3.525659317990284</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>8.320062363407128</v>
       </c>
       <c r="E98">
-        <v>-41.2724915402452</v>
+        <v>-39.73430703829681</v>
       </c>
       <c r="F98">
-        <v>-1.8039383254262</v>
+        <v>-1.196844423262498</v>
       </c>
       <c r="G98">
-        <v>-5.939570082314185</v>
+        <v>-4.187576414203244</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>8.110282168084387</v>
       </c>
       <c r="E99">
-        <v>-42.63337949208228</v>
+        <v>-41.14857664173631</v>
       </c>
       <c r="F99">
-        <v>-2.237918351018055</v>
+        <v>-1.297825723133369</v>
       </c>
       <c r="G99">
-        <v>-6.375847015661498</v>
+        <v>-3.702561629426779</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>7.742289991213546</v>
       </c>
       <c r="E100">
-        <v>-45.08840563433462</v>
+        <v>-43.47804404941498</v>
       </c>
       <c r="F100">
-        <v>-2.15726104537487</v>
+        <v>-1.608249780393261</v>
       </c>
       <c r="G100">
-        <v>-6.390181677846543</v>
+        <v>-3.96192963024652</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>7.298294510138073</v>
       </c>
       <c r="E101">
-        <v>-47.21501325612868</v>
+        <v>-44.98574739281774</v>
       </c>
       <c r="F101">
-        <v>-2.340001379534649</v>
+        <v>-1.595903792621937</v>
       </c>
       <c r="G101">
-        <v>-7.073494829879812</v>
+        <v>-4.397938409405153</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>6.660713292052234</v>
       </c>
       <c r="E102">
-        <v>-49.29747052058496</v>
+        <v>-47.65101246935018</v>
       </c>
       <c r="F102">
-        <v>-2.590319098047409</v>
+        <v>-2.11652773507701</v>
       </c>
       <c r="G102">
-        <v>-7.050546128201584</v>
+        <v>-4.732929201978465</v>
       </c>
     </row>
   </sheetData>
